--- a/data/internalStats2/File2/TC9_Exc_Internal2.xlsx
+++ b/data/internalStats2/File2/TC9_Exc_Internal2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RAO_Automation\data\internalStats2\File2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RPT_Automation\data\internalStats2\File2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91310D55-7474-460A-A420-7E44F96A990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B03C60AE-9CDD-49AD-8727-40B23377C7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE4AB3CC-D10F-42FD-B9AC-9900B0B91710}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6971FD68-8535-47B4-A472-8ED9339C43BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1B1880-D931-4117-A6B9-E0F1B77644D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCA500C-E63B-4121-98C3-064902D3E5FB}">
   <dimension ref="B2:AO706"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -16863,10 +16863,10 @@
         <v>43</v>
       </c>
       <c r="AM610">
-        <v>0.83443725292850746</v>
+        <v>0</v>
       </c>
       <c r="AN610">
-        <v>2.6596943156065567E-3</v>
+        <v>0</v>
       </c>
       <c r="AO610">
         <v>42556.368641698187</v>
